--- a/data/trans_bre/P2A_fisi_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P2A_fisi_R-Provincia-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 2,12</t>
+          <t>-3,39; 2,35</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 10,21</t>
+          <t>0,39; 10,96</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 8,29</t>
+          <t>-1,11; 7,73</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 5,14</t>
+          <t>-4,03; 4,85</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-81,49; 166,83</t>
+          <t>-80,62; 215,24</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,51; 166,42</t>
+          <t>1,65; 185,46</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-18,45; 232,12</t>
+          <t>-16,37; 210,8</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-27,81; 76,81</t>
+          <t>-31,41; 66,39</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 3,38</t>
+          <t>-4,26; 3,17</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 3,53</t>
+          <t>-3,48; 3,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 3,11</t>
+          <t>-1,76; 3,07</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,4; 2,65</t>
+          <t>-6,39; 2,86</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-38,12; 60,42</t>
+          <t>-41,96; 51,44</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-35,98; 60,58</t>
+          <t>-35,44; 53,05</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-40,37; 139,7</t>
+          <t>-42,6; 138,14</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-31,41; 18,63</t>
+          <t>-30,99; 20,85</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 3,36</t>
+          <t>-1,65; 3,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 4,78</t>
+          <t>-3,94; 4,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 4,47</t>
+          <t>-0,3; 4,31</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,43; 2,72</t>
+          <t>-6,27; 2,52</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-57,96; 253,23</t>
+          <t>-54,76; 345,71</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-38,68; 96,39</t>
+          <t>-41,01; 86,4</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-22,08; 722,83</t>
+          <t>-24,71; 584,24</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-41,88; 27,55</t>
+          <t>-40,27; 24,14</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,16; 5,38</t>
+          <t>0,13; 5,53</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 7,52</t>
+          <t>-0,49; 7,51</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 7,4</t>
+          <t>-1,8; 6,84</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-8,36; 0,32</t>
+          <t>-7,63; 0,48</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 434,71</t>
+          <t>-5,42; 462,34</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-7,13; 177,69</t>
+          <t>-11,97; 178,02</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-16,87; 116,04</t>
+          <t>-18,57; 111,34</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-75,74; 14,1</t>
+          <t>-73,6; 15,17</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 7,36</t>
+          <t>-3,88; 7,63</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 13,62</t>
+          <t>-1,19; 13,82</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,88; 4,66</t>
+          <t>-4,69; 4,99</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,81; 3,67</t>
+          <t>-5,18; 4,01</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-38,73; 125,81</t>
+          <t>-37,23; 135,86</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 146,14</t>
+          <t>-8,39; 144,74</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-53,19; 112,56</t>
+          <t>-50,05; 108,47</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-49,6; 72,24</t>
+          <t>-53,74; 79,21</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,01; 4,44</t>
+          <t>-0,01; 4,53</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 9,81</t>
+          <t>0,61; 9,95</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 6,06</t>
+          <t>-3,86; 6,04</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-7,26; 4,68</t>
+          <t>-7,23; 3,94</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-55,53; —</t>
+          <t>-58,18; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-4,06; 238,36</t>
+          <t>2,97; 236,8</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-40,91; 100,55</t>
+          <t>-37,48; 107,35</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-29,97; 26,01</t>
+          <t>-30,1; 22,8</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 2,96</t>
+          <t>-2,54; 2,59</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 3,85</t>
+          <t>-1,98; 4,22</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 4,65</t>
+          <t>-0,54; 4,66</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,66; 52,05</t>
+          <t>0,75; 56,57</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-38,12; 65,56</t>
+          <t>-38,74; 58,8</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-29,7; 74,84</t>
+          <t>-23,58; 79,62</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-11,82; 151,32</t>
+          <t>-11,53; 155,14</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5,27; 572,25</t>
+          <t>5,47; 617,87</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 5,55</t>
+          <t>0,41; 5,99</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 2,27</t>
+          <t>-2,89; 2,25</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 3,27</t>
+          <t>-2,29; 3,39</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,19; 7,69</t>
+          <t>1,11; 7,24</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 102,51</t>
+          <t>3,94; 111,17</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-39,33; 45,08</t>
+          <t>-36,18; 43,16</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-29,41; 55,56</t>
+          <t>-27,88; 62,64</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>16,54; 282,57</t>
+          <t>16,88; 291,67</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,04; 2,35</t>
+          <t>0,13; 2,4</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,28; 3,02</t>
+          <t>0,31; 3,19</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,15; 2,56</t>
+          <t>0,12; 2,6</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 21,24</t>
+          <t>-0,22; 21,97</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,62; 53,59</t>
+          <t>2,07; 52,83</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,63; 45,39</t>
+          <t>3,63; 47,04</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,38; 51,15</t>
+          <t>1,35; 50,72</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 212,75</t>
+          <t>-2,36; 250,37</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_fisi_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P2A_fisi_R-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,01</t>
+          <t>1,24</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>14,06%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 2,35</t>
+          <t>-3,21; 2,49</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,39; 10,96</t>
+          <t>0,19; 10,81</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 7,73</t>
+          <t>-1,15; 7,52</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 4,85</t>
+          <t>-2,55; 5,41</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-80,62; 215,24</t>
+          <t>-76,23; 204,14</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,65; 185,46</t>
+          <t>-1,49; 193,6</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-16,37; 210,8</t>
+          <t>-17,21; 204,13</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-31,41; 66,39</t>
+          <t>-24,02; 84,23</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-1,72</t>
+          <t>-1,83</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-10,04%</t>
+          <t>-10,71%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,26; 3,17</t>
+          <t>-3,67; 3,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 3,35</t>
+          <t>-3,48; 3,53</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 3,07</t>
+          <t>-1,4; 3,59</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,39; 2,86</t>
+          <t>-6,66; 2,55</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-41,96; 51,44</t>
+          <t>-37,99; 53,88</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-35,44; 53,05</t>
+          <t>-35,14; 59,43</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-42,6; 138,14</t>
+          <t>-36,64; 155,76</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-30,99; 20,85</t>
+          <t>-32,41; 18,14</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-1,8</t>
+          <t>-1,29</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-14,13%</t>
+          <t>-10,62%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 3,17</t>
+          <t>-1,76; 3,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,94; 4,91</t>
+          <t>-3,93; 5,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 4,31</t>
+          <t>-0,02; 4,48</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,27; 2,52</t>
+          <t>-5,71; 2,64</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-54,76; 345,71</t>
+          <t>-64,61; 294,33</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-41,01; 86,4</t>
+          <t>-40,5; 91,87</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-24,71; 584,24</t>
+          <t>-19,7; 573,97</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-40,27; 24,14</t>
+          <t>-39,49; 28,71</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-2,96</t>
+          <t>-2,07</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-43,56%</t>
+          <t>-30,34%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,13; 5,53</t>
+          <t>-0,05; 5,52</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 7,51</t>
+          <t>-0,43; 7,71</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 6,84</t>
+          <t>-1,16; 7,44</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,63; 0,48</t>
+          <t>-6,39; 1,85</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 462,34</t>
+          <t>-6,59; 403,96</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-11,97; 178,02</t>
+          <t>-7,93; 190,16</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-18,57; 111,34</t>
+          <t>-15,37; 115,93</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-73,6; 15,17</t>
+          <t>-63,18; 47,03</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0,13</t>
+          <t>1,78</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-1,78%</t>
+          <t>25,92%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 7,63</t>
+          <t>-4,38; 7,06</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 13,82</t>
+          <t>-0,46; 13,78</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,69; 4,99</t>
+          <t>-5,17; 5,24</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,18; 4,01</t>
+          <t>-2,04; 5,15</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-37,23; 135,86</t>
+          <t>-38,56; 120,69</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-8,39; 144,74</t>
+          <t>-5,21; 138,21</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-50,05; 108,47</t>
+          <t>-53,39; 120,93</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-53,74; 79,21</t>
+          <t>-23,5; 113,41</t>
         </is>
       </c>
     </row>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-7,1%</t>
+          <t>-7,18%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 4,53</t>
+          <t>-0,07; 4,51</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,61; 9,95</t>
+          <t>1,04; 10,59</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 6,04</t>
+          <t>-4,03; 6,4</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-7,23; 3,94</t>
+          <t>-6,94; 4,08</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-58,18; —</t>
+          <t>-59,8; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,97; 236,8</t>
+          <t>8,43; 259,21</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-37,48; 107,35</t>
+          <t>-37,02; 102,09</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-30,1; 22,8</t>
+          <t>-29,44; 23,34</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22,92</t>
+          <t>2,91</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>207,32%</t>
+          <t>25,64%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 2,59</t>
+          <t>-2,52; 2,58</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 4,22</t>
+          <t>-2,06; 4,35</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 4,66</t>
+          <t>-0,76; 4,35</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,75; 56,57</t>
+          <t>-0,42; 6,06</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-38,74; 58,8</t>
+          <t>-37,37; 60,79</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-23,58; 79,62</t>
+          <t>-26,37; 83,68</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-11,53; 155,14</t>
+          <t>-17,21; 136,94</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5,47; 617,87</t>
+          <t>-3,75; 60,71</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3,77</t>
+          <t>2,62</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>81,25%</t>
+          <t>42,79%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,41; 5,99</t>
+          <t>0,17; 5,9</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 2,25</t>
+          <t>-3,07; 2,16</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 3,39</t>
+          <t>-2,2; 3,51</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,11; 7,24</t>
+          <t>0,2; 4,81</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,94; 111,17</t>
+          <t>0,64; 108,86</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-36,18; 43,16</t>
+          <t>-38,33; 41,97</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-27,88; 62,64</t>
+          <t>-25,71; 58,57</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>16,88; 291,67</t>
+          <t>2,22; 99,66</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5,27</t>
+          <t>0,58</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>50,39%</t>
+          <t>5,31%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,13; 2,4</t>
+          <t>0,04; 2,4</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,31; 3,19</t>
+          <t>0,51; 3,25</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,12; 2,6</t>
+          <t>0,18; 2,52</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 21,97</t>
+          <t>-0,95; 1,88</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,07; 52,83</t>
+          <t>0,69; 54,46</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,63; 47,04</t>
+          <t>6,25; 48,27</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,35; 50,72</t>
+          <t>3,05; 51,21</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 250,37</t>
+          <t>-8,17; 18,58</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_fisi_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P2A_fisi_R-Provincia-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación por discapacidad física</t>
+          <t>Población que convive con personas con alguna limitación por discapacidad física</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
